--- a/design_tables/excel/ResourceConfig.xlsx
+++ b/design_tables/excel/ResourceConfig.xlsx
@@ -85,22 +85,6 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ResourceConfigTable" displayName="ResourceConfigTable" ref="A1:H11" headerRowCount="1">
-  <x:tableColumns count="8">
-    <x:tableColumn id="1" name="id"/>
-    <x:tableColumn id="2" name="name"/>
-    <x:tableColumn id="3" name="type"/>
-    <x:tableColumn id="4" name="default_value"/>
-    <x:tableColumn id="5" name="min_value"/>
-    <x:tableColumn id="6" name="max_value"/>
-    <x:tableColumn id="7" name="keep_after_battle"/>
-    <x:tableColumn id="8" name="comment"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -536,8 +520,5 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11fa72ec99b041ff"/>
-  </x:tableParts>
 </x:worksheet>
 </file>
--- a/design_tables/excel/ResourceConfig.xlsx
+++ b/design_tables/excel/ResourceConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResourceConfig" sheetId="1" r:id="R99451e6dc1c6446a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResourceConfig" sheetId="1" r:id="R1685812ff32f420c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,13 +21,13 @@
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FFFFFF"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="111827"/>
+      <x:color rgb="FF111827"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
@@ -40,17 +40,17 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="1F2937"/>
+        <x:fgColor rgb="FF1F2937"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="374151"/>
+        <x:fgColor rgb="FF374151"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="E5E7EB"/>
+        <x:fgColor rgb="FFE5E7EB"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -274,68 +274,64 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>string</x:v>
+        <x:v>hp</x:v>
       </x:c>
       <x:c r="B2" s="6" t="str">
-        <x:v>string</x:v>
+        <x:v>生命值</x:v>
       </x:c>
       <x:c r="C2" s="6" t="str">
-        <x:v>string</x:v>
+        <x:v>核心资源</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>string</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="F2" s="6" t="str">
-        <x:v>string</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F2" s="6" t="str"/>
       <x:c r="G2" s="6" t="str">
-        <x:v>bool</x:v>
+        <x:v>false</x:v>
       </x:c>
       <x:c r="H2" s="6" t="str">
-        <x:v>string</x:v>
+        <x:v>生命值为0或以下时失败</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="25.5" customHeight="1">
       <x:c r="A3" s="9" t="str">
-        <x:v>资源ID</x:v>
+        <x:v>magic</x:v>
       </x:c>
       <x:c r="B3" s="9" t="str">
-        <x:v>资源名称</x:v>
+        <x:v>魔力</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
-        <x:v>资源类型</x:v>
+        <x:v>回合资源</x:v>
       </x:c>
       <x:c r="D3" s="9" t="str">
-        <x:v>默认值</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E3" s="9" t="str">
-        <x:v>最小值</x:v>
-      </x:c>
-      <x:c r="F3" s="9" t="str">
-        <x:v>最大值</x:v>
-      </x:c>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F3" s="9" t="str"/>
       <x:c r="G3" s="9" t="str">
-        <x:v>战斗结束是否保留</x:v>
+        <x:v>false</x:v>
       </x:c>
       <x:c r="H3" s="9" t="str">
-        <x:v>说明</x:v>
+        <x:v>当前回合出牌资源</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="25.5" customHeight="1">
       <x:c r="A4" s="10" t="str">
-        <x:v>hp</x:v>
+        <x:v>magic_max</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>生命值</x:v>
+        <x:v>魔力上限</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>核心资源</x:v>
+        <x:v>形态资源</x:v>
       </x:c>
       <x:c r="D4" s="10" t="str">
-        <x:v>70</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E4" s="10" t="str">
         <x:v>0</x:v>
@@ -345,18 +341,18 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="H4" s="10" t="str">
-        <x:v>生命值为0或以下时失败</x:v>
+        <x:v>决定回合开始恢复多少魔力</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="25.5" customHeight="1">
       <x:c r="A5" s="10" t="str">
-        <x:v>magic</x:v>
+        <x:v>magic_shield</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>魔力</x:v>
+        <x:v>魔力护盾</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>回合资源</x:v>
+        <x:v>防御资源</x:v>
       </x:c>
       <x:c r="D5" s="10" t="str">
         <x:v>0</x:v>
@@ -369,18 +365,18 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="H5" s="10" t="str">
-        <x:v>当前回合出牌资源</x:v>
+        <x:v>先于魔力防御抵挡普通伤害</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="25.5" customHeight="1">
       <x:c r="A6" s="10" t="str">
-        <x:v>magic_max</x:v>
+        <x:v>magic_defense</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>魔力上限</x:v>
+        <x:v>魔力防御</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
-        <x:v>形态资源</x:v>
+        <x:v>变身耐久</x:v>
       </x:c>
       <x:c r="D6" s="10" t="str">
         <x:v>0</x:v>
@@ -393,18 +389,18 @@
         <x:v>false</x:v>
       </x:c>
       <x:c r="H6" s="10" t="str">
-        <x:v>决定回合开始恢复多少魔力</x:v>
+        <x:v>归零时解除变身</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="25.5" customHeight="1">
       <x:c r="A7" s="10" t="str">
-        <x:v>magic_shield</x:v>
+        <x:v>arousal</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>魔力护盾</x:v>
+        <x:v>发情值</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
-        <x:v>防御资源</x:v>
+        <x:v>特殊属性</x:v>
       </x:c>
       <x:c r="D7" s="10" t="str">
         <x:v>0</x:v>
@@ -412,23 +408,27 @@
       <x:c r="E7" s="10" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F7" s="10" t="str"/>
+      <x:c r="F7" s="10" t="str">
+        <x:v>100</x:v>
+      </x:c>
       <x:c r="G7" s="10" t="str">
-        <x:v>false</x:v>
-      </x:c>
-      <x:c r="H7" s="10" t="str">
-        <x:v>先于魔力防御抵挡普通伤害</x:v>
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>用于卡牌条件和其他效果结算</t>
+        </is>
       </x:c>
     </x:row>
     <x:row r="8" ht="25.5" customHeight="1">
       <x:c r="A8" s="10" t="str">
-        <x:v>magic_defense</x:v>
+        <x:v>sensitivity</x:v>
       </x:c>
       <x:c r="B8" s="10" t="str">
-        <x:v>魔力防御</x:v>
+        <x:v>敏感值</x:v>
       </x:c>
       <x:c r="C8" s="10" t="str">
-        <x:v>变身耐久</x:v>
+        <x:v>特殊属性</x:v>
       </x:c>
       <x:c r="D8" s="10" t="str">
         <x:v>0</x:v>
@@ -438,18 +438,18 @@
       </x:c>
       <x:c r="F8" s="10" t="str"/>
       <x:c r="G8" s="10" t="str">
-        <x:v>false</x:v>
+        <x:v>true</x:v>
       </x:c>
       <x:c r="H8" s="10" t="str">
-        <x:v>归零时解除变身</x:v>
+        <x:v>放大获得的发情值</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="25.5" customHeight="1">
       <x:c r="A9" s="10" t="str">
-        <x:v>arousal</x:v>
+        <x:v>corruption</x:v>
       </x:c>
       <x:c r="B9" s="10" t="str">
-        <x:v>发情值</x:v>
+        <x:v>堕落值</x:v>
       </x:c>
       <x:c r="C9" s="10" t="str">
         <x:v>特殊属性</x:v>
@@ -460,25 +460,23 @@
       <x:c r="E9" s="10" t="str">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F9" s="10" t="str">
-        <x:v>100</x:v>
-      </x:c>
+      <x:c r="F9" s="10" t="str"/>
       <x:c r="G9" s="10" t="str">
         <x:v>true</x:v>
       </x:c>
       <x:c r="H9" s="10" t="str">
-        <x:v>影响魔力伤害和魅惑伤害</x:v>
+        <x:v>影响卡牌和选项使用条件</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="25.5" customHeight="1">
       <x:c r="A10" s="10" t="str">
-        <x:v>sensitivity</x:v>
+        <x:v>masochism_tendency</x:v>
       </x:c>
       <x:c r="B10" s="10" t="str">
-        <x:v>敏感值</x:v>
+        <x:v>受虐倾向</x:v>
       </x:c>
       <x:c r="C10" s="10" t="str">
-        <x:v>特殊属性</x:v>
+        <x:v>人物属性</x:v>
       </x:c>
       <x:c r="D10" s="10" t="str">
         <x:v>0</x:v>
@@ -491,18 +489,18 @@
         <x:v>true</x:v>
       </x:c>
       <x:c r="H10" s="10" t="str">
-        <x:v>放大获得的发情值</x:v>
+        <x:v>影响选项和对应攻击造成的发情变化</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="25.5" customHeight="1">
       <x:c r="A11" s="10" t="str">
-        <x:v>corruption</x:v>
+        <x:v>exposure_tendency</x:v>
       </x:c>
       <x:c r="B11" s="10" t="str">
-        <x:v>堕落值</x:v>
+        <x:v>暴露倾向</x:v>
       </x:c>
       <x:c r="C11" s="10" t="str">
-        <x:v>特殊属性</x:v>
+        <x:v>人物属性</x:v>
       </x:c>
       <x:c r="D11" s="10" t="str">
         <x:v>0</x:v>
@@ -515,7 +513,195 @@
         <x:v>true</x:v>
       </x:c>
       <x:c r="H11" s="10" t="str">
-        <x:v>影响卡牌和选项使用条件</x:v>
+        <x:v>影响选项和暴露标签攻击造成的发情变化</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>kiss_tendency</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>接吻倾向</x:v>
+      </x:c>
+      <x:c r="C12" t="str">
+        <x:v>人物属性</x:v>
+      </x:c>
+      <x:c r="D12" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E12" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F12" t="str"/>
+      <x:c r="G12" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
+        <x:v>影响选项和接吻标签攻击造成的发情变化</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>semen</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>子宫精液含量</x:v>
+      </x:c>
+      <x:c r="C13" t="str">
+        <x:v>特殊资源</x:v>
+      </x:c>
+      <x:c r="D13" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" t="str"/>
+      <x:c r="G13" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
+        <x:v>后续用于支付、溢出、泄漏和转化魔力</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>chest_sensitivity</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>胸部敏感度</x:v>
+      </x:c>
+      <x:c r="C14" t="str">
+        <x:v>部位敏感度</x:v>
+      </x:c>
+      <x:c r="D14" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E14" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F14" t="str"/>
+      <x:c r="G14" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
+        <x:v>胸部标签攻击会额外提升发情值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>clitoris_sensitivity</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>阴蒂敏感度</x:v>
+      </x:c>
+      <x:c r="C15" t="str">
+        <x:v>部位敏感度</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" t="str"/>
+      <x:c r="G15" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>阴蒂标签攻击会额外提升发情值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>womb_sensitivity</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>子宫敏感度</x:v>
+      </x:c>
+      <x:c r="C16" t="str">
+        <x:v>部位敏感度</x:v>
+      </x:c>
+      <x:c r="D16" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" t="str"/>
+      <x:c r="G16" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="H16" t="str">
+        <x:v>子宫标签攻击会额外提升发情值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>vagina_sensitivity</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>小穴敏感度</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>部位敏感度</x:v>
+      </x:c>
+      <x:c r="D17" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" t="str"/>
+      <x:c r="G17" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>小穴标签攻击会额外提升发情值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>firepower</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>火力</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>战斗属性</x:v>
+      </x:c>
+      <x:c r="D18" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" t="str"/>
+      <x:c r="F18" t="str"/>
+      <x:c r="G18" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>修正通过造成伤害效果结算的伤害；正数提高，负数降低</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>spirit</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>灵力</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>战斗属性</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E19" t="str"/>
+      <x:c r="F19" t="str"/>
+      <x:c r="G19" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>修正获得魔力护盾的数值；正数提高，负数降低</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
